--- a/tools/importer/reports/import-content.report.xlsx
+++ b/tools/importer/reports/import-content.report.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="520" uniqueCount="346">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="712" uniqueCount="469">
   <si>
     <t>_reportFile</t>
   </si>
@@ -70,7 +70,7 @@
     <t>content</t>
   </si>
   <si>
-    <t>2026-06-19T00:49:43.591Z</t>
+    <t>2026-06-22T15:55:21.180Z</t>
   </si>
   <si>
     <t>https://www.avg.com/en-us/activate-account</t>
@@ -187,7 +187,7 @@
     <t>avg/en-us/avg-go-tech-support</t>
   </si>
   <si>
-    <t>2026-06-19T00:49:56.751Z</t>
+    <t>2026-06-22T15:55:34.428Z</t>
   </si>
   <si>
     <t>Get Tech Support for Any Device | AVG Go | Free Diagnosis</t>
@@ -427,7 +427,7 @@
     <t>avg/en-us/contacts</t>
   </si>
   <si>
-    <t>2026-06-19T00:51:01.319Z</t>
+    <t>2026-06-22T15:56:40.465Z</t>
   </si>
   <si>
     <t>Contact Us | AVG</t>
@@ -475,7 +475,7 @@
     <t>avg/en-us/download-secure-vpn-android</t>
   </si>
   <si>
-    <t>2026-06-19T00:47:41.665Z</t>
+    <t>2026-06-19T00:59:24.037Z</t>
   </si>
   <si>
     <t>VPN For Android | Download Free Trial | AVG Secure VPN</t>
@@ -484,6 +484,39 @@
     <t>https://www.avg.com/en-us/download-secure-vpn-android</t>
   </si>
   <si>
+    <t>avg/en-us/download-secure-vpn-ios.report.json</t>
+  </si>
+  <si>
+    <t>avg/en-us/download-secure-vpn-ios</t>
+  </si>
+  <si>
+    <t>2026-06-19T01:00:16.096Z</t>
+  </si>
+  <si>
+    <t>Download a Free Trial of AVG VPN For iOS | AVG Secure VPN</t>
+  </si>
+  <si>
+    <t>https://www.avg.com/en-us/download-secure-vpn-ios</t>
+  </si>
+  <si>
+    <t>avg/en-us/download-secure-vpn-mac.report.json</t>
+  </si>
+  <si>
+    <t>["promo-bar","columns-feature","carousel-blog"]</t>
+  </si>
+  <si>
+    <t>avg/en-us/download-secure-vpn-mac</t>
+  </si>
+  <si>
+    <t>2026-06-19T01:01:10.271Z</t>
+  </si>
+  <si>
+    <t>Free VPN Download for Mac</t>
+  </si>
+  <si>
+    <t>https://www.avg.com/en-us/download-secure-vpn-mac</t>
+  </si>
+  <si>
     <t>avg/en-us/email-server-business-edition.report.json</t>
   </si>
   <si>
@@ -523,7 +556,7 @@
     <t>avg/en-us/eula</t>
   </si>
   <si>
-    <t>2026-06-19T00:52:01.180Z</t>
+    <t>2026-06-22T15:54:25.976Z</t>
   </si>
   <si>
     <t>End user license agreements | AVG</t>
@@ -550,13 +583,28 @@
     <t>https://www.avg.com/en-us/file-server-business-edition</t>
   </si>
   <si>
+    <t>avg/en-us/free-antivirus-download.report.json</t>
+  </si>
+  <si>
+    <t>avg/en-us/free-antivirus-download</t>
+  </si>
+  <si>
+    <t>2026-06-19T01:02:03.863Z</t>
+  </si>
+  <si>
+    <t>Download Free Antivirus Software for PC | AVG Virus Protection</t>
+  </si>
+  <si>
+    <t>https://www.avg.com/en-us/free-antivirus-download</t>
+  </si>
+  <si>
     <t>avg/en-us/hackers-and-hacking.report.json</t>
   </si>
   <si>
     <t>avg/en-us/hackers-and-hacking</t>
   </si>
   <si>
-    <t>2026-06-19T00:51:54.161Z</t>
+    <t>2026-06-22T15:57:33.423Z</t>
   </si>
   <si>
     <t>Hackers and Hacking | Free eBook from AVG SMB</t>
@@ -604,6 +652,21 @@
     <t>https://www.avg.com/en-us/homepage</t>
   </si>
   <si>
+    <t>avg/en-us/internet-security-be-demo.report.json</t>
+  </si>
+  <si>
+    <t>avg/en-us/internet-security-be-demo</t>
+  </si>
+  <si>
+    <t>2026-06-19T01:03:02.749Z</t>
+  </si>
+  <si>
+    <t>AVG Business Internet Security | Online Security for Businesses</t>
+  </si>
+  <si>
+    <t>https://www.avg.com/en-us/internet-security-be-demo</t>
+  </si>
+  <si>
     <t>avg/en-us/internet-security-business-edition.report.json</t>
   </si>
   <si>
@@ -619,13 +682,43 @@
     <t>https://www.avg.com/en-us/internet-security-business-edition</t>
   </si>
   <si>
+    <t>avg/en-us/internet-security-for-mac.report.json</t>
+  </si>
+  <si>
+    <t>avg/en-us/internet-security-for-mac</t>
+  </si>
+  <si>
+    <t>2026-06-19T01:03:56.196Z</t>
+  </si>
+  <si>
+    <t>AVG Internet Security for Mac | Mac Security Software</t>
+  </si>
+  <si>
+    <t>https://www.avg.com/en-us/internet-security-for-mac</t>
+  </si>
+  <si>
+    <t>avg/en-us/internet-security.report.json</t>
+  </si>
+  <si>
+    <t>avg/en-us/internet-security</t>
+  </si>
+  <si>
+    <t>2026-06-19T01:02:10.228Z</t>
+  </si>
+  <si>
+    <t>AVG Internet Security Software | Online Protection | Free Trial</t>
+  </si>
+  <si>
+    <t>https://www.avg.com/en-us/internet-security</t>
+  </si>
+  <si>
     <t>avg/en-us/keeping-your-data-safe.report.json</t>
   </si>
   <si>
     <t>avg/en-us/keeping-your-data-safe</t>
   </si>
   <si>
-    <t>2026-06-19T00:52:00.998Z</t>
+    <t>2026-06-22T15:57:39.680Z</t>
   </si>
   <si>
     <t>Keeping Your Data Safe | Free eBook from AVG SMB</t>
@@ -667,6 +760,21 @@
     <t>https://www.avg.com/en-us/management-console</t>
   </si>
   <si>
+    <t>avg/en-us/mobile-security-for-iphone-ipad.report.json</t>
+  </si>
+  <si>
+    <t>avg/en-us/mobile-security-for-iphone-ipad</t>
+  </si>
+  <si>
+    <t>2026-06-19T01:04:49.757Z</t>
+  </si>
+  <si>
+    <t>Free Antivirus App for iPhone and iPad | AVG Mobile Security</t>
+  </si>
+  <si>
+    <t>https://www.avg.com/en-us/mobile-security-for-iphone-ipad</t>
+  </si>
+  <si>
     <t>avg/en-us/online-markets-by-country.report.json</t>
   </si>
   <si>
@@ -721,7 +829,7 @@
     <t>avg/en-us/online-security-plugin</t>
   </si>
   <si>
-    <t>2026-06-19T00:52:54.193Z</t>
+    <t>2026-06-22T15:58:33.050Z</t>
   </si>
   <si>
     <t>AVG Online Security Plugin | Free Browser Security Extension</t>
@@ -736,7 +844,7 @@
     <t>avg/en-us/partners</t>
   </si>
   <si>
-    <t>2026-06-19T00:53:46.999Z</t>
+    <t>2026-06-22T15:59:25.738Z</t>
   </si>
   <si>
     <t>Partner with the Global Leader in Security | AVG Business</t>
@@ -826,7 +934,7 @@
     <t>avg/en-us/profile</t>
   </si>
   <si>
-    <t>2026-06-19T00:54:40.227Z</t>
+    <t>2026-06-22T16:00:17.051Z</t>
   </si>
   <si>
     <t>Profile | AVG Technologies</t>
@@ -844,7 +952,7 @@
     <t>avg/en-us/random-password-generator</t>
   </si>
   <si>
-    <t>2026-06-19T00:54:09.140Z</t>
+    <t>2026-06-22T15:53:20.622Z</t>
   </si>
   <si>
     <t>Random Password Generator | Free Online Tool | AVG</t>
@@ -889,7 +997,7 @@
     <t>avg/en-us/remove-win32-expiro</t>
   </si>
   <si>
-    <t>2026-06-19T00:55:34.164Z</t>
+    <t>2026-06-22T16:01:11.649Z</t>
   </si>
   <si>
     <t>How to Remove Win32/Expiro in 3 Easy Steps | AVG</t>
@@ -904,7 +1012,7 @@
     <t>avg/en-us/remove-win32-neshta</t>
   </si>
   <si>
-    <t>2026-06-19T00:56:27.932Z</t>
+    <t>2026-06-22T16:02:03.937Z</t>
   </si>
   <si>
     <t>How to Remove Win32/Neshta in 3 Easy Steps | AVG</t>
@@ -919,7 +1027,7 @@
     <t>avg/en-us/remove-win32-virut</t>
   </si>
   <si>
-    <t>2026-06-19T00:57:20.566Z</t>
+    <t>2026-06-22T16:02:56.968Z</t>
   </si>
   <si>
     <t>How to Remove Win32/Virut in 3 Easy Steps | AVG</t>
@@ -943,13 +1051,61 @@
     <t>https://www.avg.com/en-us/research-participant-terms-conditions</t>
   </si>
   <si>
+    <t>avg/en-us/secure-browser.report.json</t>
+  </si>
+  <si>
+    <t>avg/en-us/secure-browser</t>
+  </si>
+  <si>
+    <t>2026-06-19T01:05:43.279Z</t>
+  </si>
+  <si>
+    <t>Download Our Free Private Web Browser | AVG Secure Browser</t>
+  </si>
+  <si>
+    <t>https://www.avg.com/en-us/secure-browser</t>
+  </si>
+  <si>
+    <t>avg/en-us/secure-vpn-acceptable-use.report.json</t>
+  </si>
+  <si>
+    <t>avg/en-us/secure-vpn-acceptable-use</t>
+  </si>
+  <si>
+    <t>2026-06-19T00:59:54.993Z</t>
+  </si>
+  <si>
+    <t>AVG | Secure VPN Acceptable Use</t>
+  </si>
+  <si>
+    <t>https://www.avg.com/en-us/secure-vpn-acceptable-use</t>
+  </si>
+  <si>
+    <t>avg/en-us/secure-vpn.report.json</t>
+  </si>
+  <si>
+    <t>["promo-bar","hero-product","rating","card-pricing","usp-stripe","card-feature","columns-feature","columns-feature","columns-feature","columns-feature","columns-feature","columns-feature","columns-feature","columns-feature","steps","accordion-faq","carousel-blog"]</t>
+  </si>
+  <si>
+    <t>avg/en-us/secure-vpn</t>
+  </si>
+  <si>
+    <t>2026-06-22T15:53:33.121Z</t>
+  </si>
+  <si>
+    <t>Download Secure VPN for PC or Laptop | Free Trial | AVG</t>
+  </si>
+  <si>
+    <t>https://www.avg.com/en-us/secure-vpn</t>
+  </si>
+  <si>
     <t>avg/en-us/services.report.json</t>
   </si>
   <si>
     <t>avg/en-us/services</t>
   </si>
   <si>
-    <t>2026-06-19T00:58:13.151Z</t>
+    <t>2026-06-22T16:03:50.431Z</t>
   </si>
   <si>
     <t>https://www.avg.com/en-us/services</t>
@@ -985,13 +1141,28 @@
     <t>https://www.avg.com/en-us/store-business</t>
   </si>
   <si>
+    <t>avg/en-us/store.report.json</t>
+  </si>
+  <si>
+    <t>avg/en-us/store</t>
+  </si>
+  <si>
+    <t>2026-06-19T01:07:29.540Z</t>
+  </si>
+  <si>
+    <t>AVG Store | Explore all Products &amp; Prices | Buy AVG Now!</t>
+  </si>
+  <si>
+    <t>https://www.avg.com/en-us/store</t>
+  </si>
+  <si>
     <t>avg/en-us/submit-a-sample.report.json</t>
   </si>
   <si>
     <t>avg/en-us/submit-a-sample</t>
   </si>
   <si>
-    <t>2026-06-19T00:59:04.654Z</t>
+    <t>2026-06-22T16:04:42.160Z</t>
   </si>
   <si>
     <t>Choose Your Sample Submission Type | AVG</t>
@@ -1000,13 +1171,211 @@
     <t>https://www.avg.com/en-us/submit-a-sample</t>
   </si>
   <si>
+    <t>avg/en-us/subscription-details.report.json</t>
+  </si>
+  <si>
+    <t>avg/en-us/subscription-details</t>
+  </si>
+  <si>
+    <t>2026-06-19T01:00:47.165Z</t>
+  </si>
+  <si>
+    <t>Subscription details</t>
+  </si>
+  <si>
+    <t>https://www.avg.com/en-us/subscription-details</t>
+  </si>
+  <si>
+    <t>avg/en-us/supplier-guidelines.report.json</t>
+  </si>
+  <si>
+    <t>avg/en-us/supplier-guidelines</t>
+  </si>
+  <si>
+    <t>2026-06-19T01:01:48.946Z</t>
+  </si>
+  <si>
+    <t>AVG Supplier Guidelines</t>
+  </si>
+  <si>
+    <t>https://www.avg.com/en-us/supplier-guidelines</t>
+  </si>
+  <si>
+    <t>avg/en-us/supplier.report.json</t>
+  </si>
+  <si>
+    <t>avg/en-us/supplier</t>
+  </si>
+  <si>
+    <t>2026-06-19T01:01:40.084Z</t>
+  </si>
+  <si>
+    <t>AVG | Supporting supplier documentation</t>
+  </si>
+  <si>
+    <t>https://www.avg.com/en-us/supplier</t>
+  </si>
+  <si>
+    <t>avg/en-us/trademarks.report.json</t>
+  </si>
+  <si>
+    <t>avg/en-us/trademarks</t>
+  </si>
+  <si>
+    <t>2026-06-19T01:02:42.330Z</t>
+  </si>
+  <si>
+    <t>Third Party Copyrights &amp; Trademarks</t>
+  </si>
+  <si>
+    <t>https://www.avg.com/en-us/trademarks</t>
+  </si>
+  <si>
+    <t>avg/en-us/tuneup-software-updater.report.json</t>
+  </si>
+  <si>
+    <t>avg/en-us/tuneup-software-updater</t>
+  </si>
+  <si>
+    <t>2026-06-19T01:08:22.126Z</t>
+  </si>
+  <si>
+    <t>Update Software Automatically | AVG Software Updater for PC</t>
+  </si>
+  <si>
+    <t>https://www.avg.com/en-us/tuneup-software-updater</t>
+  </si>
+  <si>
+    <t>avg/en-us/ultimate.report.json</t>
+  </si>
+  <si>
+    <t>avg/en-us/ultimate</t>
+  </si>
+  <si>
+    <t>2026-06-19T01:09:15.715Z</t>
+  </si>
+  <si>
+    <t>AVG Ultimate | Multi-device Antivirus, Performance &amp; VPN Bundle</t>
+  </si>
+  <si>
+    <t>https://www.avg.com/en-us/ultimate</t>
+  </si>
+  <si>
+    <t>avg/en-us/vpn-dmca.report.json</t>
+  </si>
+  <si>
+    <t>avg/en-us/vpn-dmca</t>
+  </si>
+  <si>
+    <t>2026-06-19T01:03:37.095Z</t>
+  </si>
+  <si>
+    <t>DMCA | AVG Safe Surf</t>
+  </si>
+  <si>
+    <t>https://www.avg.com/en-us/vpn-dmca</t>
+  </si>
+  <si>
+    <t>avg/en-us/vpn-policy.report.json</t>
+  </si>
+  <si>
+    <t>avg/en-us/vpn-policy</t>
+  </si>
+  <si>
+    <t>2026-06-19T01:04:28.877Z</t>
+  </si>
+  <si>
+    <t>VPN Policy | We are serious about your privacy | AVG</t>
+  </si>
+  <si>
+    <t>https://www.avg.com/en-us/vpn-policy</t>
+  </si>
+  <si>
+    <t>avg/en-us/vpn-territory.report.json</t>
+  </si>
+  <si>
+    <t>avg/en-us/vpn-territory</t>
+  </si>
+  <si>
+    <t>2026-06-19T01:05:21.445Z</t>
+  </si>
+  <si>
+    <t>VPN Territory</t>
+  </si>
+  <si>
+    <t>https://www.avg.com/en-us/vpn-territory</t>
+  </si>
+  <si>
+    <t>avg/en-us/windows-10-antivirus.report.json</t>
+  </si>
+  <si>
+    <t>avg/en-us/windows-10-antivirus</t>
+  </si>
+  <si>
+    <t>2026-06-19T01:10:08.717Z</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Download Free Antivirus Software for Windows 10 PC | AVG </t>
+  </si>
+  <si>
+    <t>https://www.avg.com/en-us/windows-10-antivirus</t>
+  </si>
+  <si>
+    <t>avg/en-us/windows-11-antivirus.report.json</t>
+  </si>
+  <si>
+    <t>avg/en-us/windows-11-antivirus</t>
+  </si>
+  <si>
+    <t>2026-06-19T01:11:00.635Z</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Download AVG AntiVirus FREE for Windows 11 PCs | AVG </t>
+  </si>
+  <si>
+    <t>https://www.avg.com/en-us/windows-11-antivirus</t>
+  </si>
+  <si>
+    <t>avg/en-us/windows-7-antivirus.report.json</t>
+  </si>
+  <si>
+    <t>["columns-feature"]</t>
+  </si>
+  <si>
+    <t>avg/en-us/windows-7-antivirus</t>
+  </si>
+  <si>
+    <t>2026-06-19T01:11:53.501Z</t>
+  </si>
+  <si>
+    <t>Free Antivirus for Windows 7 | PC Virus Scan Software | AVG</t>
+  </si>
+  <si>
+    <t>https://www.avg.com/en-us/windows-7-antivirus</t>
+  </si>
+  <si>
+    <t>avg/en-us/windows-8-antivirus.report.json</t>
+  </si>
+  <si>
+    <t>avg/en-us/windows-8-antivirus</t>
+  </si>
+  <si>
+    <t>2026-06-19T01:12:46.007Z</t>
+  </si>
+  <si>
+    <t>Antivirus for Windows 8 | AVG Free Download</t>
+  </si>
+  <si>
+    <t>https://www.avg.com/en-us/windows-8-antivirus</t>
+  </si>
+  <si>
     <t>avg/en-us/affiliate/become-an-avg-affiliate.report.json</t>
   </si>
   <si>
     <t>avg/en-us/affiliate/become-an-avg-affiliate</t>
   </si>
   <si>
-    <t>2026-06-19T00:49:48.943Z</t>
+    <t>2026-06-22T15:55:27.654Z</t>
   </si>
   <si>
     <t>Become an AVG affiliate</t>
@@ -1021,7 +1390,7 @@
     <t>avg/en-us/campaign-landing-pages/ransomware-infographic-download</t>
   </si>
   <si>
-    <t>2026-06-19T00:50:02.544Z</t>
+    <t>2026-06-22T15:55:40.709Z</t>
   </si>
   <si>
     <t>https://www.avg.com/en-us/campaign-landing-pages/ransomware-infographic-download</t>
@@ -1033,7 +1402,7 @@
     <t>avg/en-us/campaign-landing-pages/ransomware-kit-download</t>
   </si>
   <si>
-    <t>2026-06-19T00:50:09.032Z</t>
+    <t>2026-06-22T15:55:46.968Z</t>
   </si>
   <si>
     <t>https://www.avg.com/en-us/campaign-landing-pages/ransomware-kit-download</t>
@@ -1437,7 +1806,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H65"/>
+  <dimension ref="A1:H89"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="3" width="50" customWidth="1"/>
@@ -2179,33 +2548,33 @@
         <v>157</v>
       </c>
       <c r="B29" t="s">
+        <v>152</v>
+      </c>
+      <c r="C29" t="s">
         <v>158</v>
       </c>
-      <c r="C29" t="s">
+      <c r="D29" t="s">
+        <v>11</v>
+      </c>
+      <c r="E29" t="s">
+        <v>24</v>
+      </c>
+      <c r="F29" t="s">
         <v>159</v>
       </c>
-      <c r="D29" t="s">
-        <v>11</v>
-      </c>
-      <c r="E29" t="s">
-        <v>30</v>
-      </c>
-      <c r="F29" t="s">
+      <c r="G29" t="s">
         <v>160</v>
       </c>
-      <c r="G29" t="s">
+      <c r="H29" t="s">
         <v>161</v>
-      </c>
-      <c r="H29" t="s">
-        <v>162</v>
       </c>
     </row>
     <row r="30" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
+        <v>162</v>
+      </c>
+      <c r="B30" t="s">
         <v>163</v>
-      </c>
-      <c r="B30" t="s">
-        <v>9</v>
       </c>
       <c r="C30" t="s">
         <v>164</v>
@@ -2214,7 +2583,7 @@
         <v>11</v>
       </c>
       <c r="E30" t="s">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="F30" t="s">
         <v>165</v>
@@ -2231,33 +2600,33 @@
         <v>168</v>
       </c>
       <c r="B31" t="s">
-        <v>9</v>
+        <v>169</v>
       </c>
       <c r="C31" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="D31" t="s">
         <v>11</v>
       </c>
       <c r="E31" t="s">
-        <v>12</v>
+        <v>30</v>
       </c>
       <c r="F31" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="G31" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="H31" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
     </row>
     <row r="32" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="B32" t="s">
-        <v>174</v>
+        <v>9</v>
       </c>
       <c r="C32" t="s">
         <v>175</v>
@@ -2292,7 +2661,7 @@
         <v>11</v>
       </c>
       <c r="E33" t="s">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="F33" t="s">
         <v>181</v>
@@ -2318,7 +2687,7 @@
         <v>11</v>
       </c>
       <c r="E34" t="s">
-        <v>91</v>
+        <v>30</v>
       </c>
       <c r="F34" t="s">
         <v>187</v>
@@ -2335,85 +2704,85 @@
         <v>190</v>
       </c>
       <c r="B35" t="s">
+        <v>22</v>
+      </c>
+      <c r="C35" t="s">
         <v>191</v>
       </c>
-      <c r="C35" t="s">
+      <c r="D35" t="s">
+        <v>11</v>
+      </c>
+      <c r="E35" t="s">
+        <v>24</v>
+      </c>
+      <c r="F35" t="s">
         <v>192</v>
       </c>
-      <c r="D35" t="s">
-        <v>11</v>
-      </c>
-      <c r="E35" t="s">
+      <c r="G35" t="s">
         <v>193</v>
       </c>
-      <c r="F35" t="s">
+      <c r="H35" t="s">
         <v>194</v>
-      </c>
-      <c r="G35" t="s">
-        <v>195</v>
-      </c>
-      <c r="H35" t="s">
-        <v>196</v>
       </c>
     </row>
     <row r="36" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
+        <v>195</v>
+      </c>
+      <c r="B36" t="s">
+        <v>9</v>
+      </c>
+      <c r="C36" t="s">
+        <v>196</v>
+      </c>
+      <c r="D36" t="s">
+        <v>11</v>
+      </c>
+      <c r="E36" t="s">
+        <v>18</v>
+      </c>
+      <c r="F36" t="s">
         <v>197</v>
       </c>
-      <c r="B36" t="s">
-        <v>9</v>
-      </c>
-      <c r="C36" t="s">
+      <c r="G36" t="s">
         <v>198</v>
       </c>
-      <c r="D36" t="s">
-        <v>11</v>
-      </c>
-      <c r="E36" t="s">
-        <v>30</v>
-      </c>
-      <c r="F36" t="s">
+      <c r="H36" t="s">
         <v>199</v>
-      </c>
-      <c r="G36" t="s">
-        <v>200</v>
-      </c>
-      <c r="H36" t="s">
-        <v>201</v>
       </c>
     </row>
     <row r="37" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
+        <v>200</v>
+      </c>
+      <c r="B37" t="s">
+        <v>201</v>
+      </c>
+      <c r="C37" t="s">
         <v>202</v>
       </c>
-      <c r="B37" t="s">
-        <v>9</v>
-      </c>
-      <c r="C37" t="s">
+      <c r="D37" t="s">
+        <v>11</v>
+      </c>
+      <c r="E37" t="s">
+        <v>91</v>
+      </c>
+      <c r="F37" t="s">
         <v>203</v>
       </c>
-      <c r="D37" t="s">
-        <v>11</v>
-      </c>
-      <c r="E37" t="s">
-        <v>18</v>
-      </c>
-      <c r="F37" t="s">
+      <c r="G37" t="s">
         <v>204</v>
       </c>
-      <c r="G37" t="s">
+      <c r="H37" t="s">
         <v>205</v>
-      </c>
-      <c r="H37" t="s">
-        <v>206</v>
       </c>
     </row>
     <row r="38" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
+        <v>206</v>
+      </c>
+      <c r="B38" t="s">
         <v>207</v>
-      </c>
-      <c r="B38" t="s">
-        <v>9</v>
       </c>
       <c r="C38" t="s">
         <v>208</v>
@@ -2422,24 +2791,24 @@
         <v>11</v>
       </c>
       <c r="E38" t="s">
-        <v>12</v>
+        <v>209</v>
       </c>
       <c r="F38" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="G38" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="H38" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
     </row>
     <row r="39" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="B39" t="s">
-        <v>213</v>
+        <v>9</v>
       </c>
       <c r="C39" t="s">
         <v>214</v>
@@ -2448,7 +2817,7 @@
         <v>11</v>
       </c>
       <c r="E39" t="s">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="F39" t="s">
         <v>215</v>
@@ -2474,7 +2843,7 @@
         <v>11</v>
       </c>
       <c r="E40" t="s">
-        <v>91</v>
+        <v>30</v>
       </c>
       <c r="F40" t="s">
         <v>220</v>
@@ -2491,62 +2860,62 @@
         <v>223</v>
       </c>
       <c r="B41" t="s">
+        <v>41</v>
+      </c>
+      <c r="C41" t="s">
         <v>224</v>
       </c>
-      <c r="C41" t="s">
+      <c r="D41" t="s">
+        <v>11</v>
+      </c>
+      <c r="E41" t="s">
+        <v>24</v>
+      </c>
+      <c r="F41" t="s">
         <v>225</v>
       </c>
-      <c r="D41" t="s">
-        <v>11</v>
-      </c>
-      <c r="E41" t="s">
-        <v>91</v>
-      </c>
-      <c r="F41" t="s">
+      <c r="G41" t="s">
         <v>226</v>
       </c>
-      <c r="G41" t="s">
+      <c r="H41" t="s">
         <v>227</v>
-      </c>
-      <c r="H41" t="s">
-        <v>228</v>
       </c>
     </row>
     <row r="42" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
+        <v>228</v>
+      </c>
+      <c r="B42" t="s">
+        <v>41</v>
+      </c>
+      <c r="C42" t="s">
         <v>229</v>
       </c>
-      <c r="B42" t="s">
+      <c r="D42" t="s">
+        <v>11</v>
+      </c>
+      <c r="E42" t="s">
+        <v>24</v>
+      </c>
+      <c r="F42" t="s">
         <v>230</v>
       </c>
-      <c r="C42" t="s">
+      <c r="G42" t="s">
         <v>231</v>
       </c>
-      <c r="D42" t="s">
-        <v>11</v>
-      </c>
-      <c r="E42" t="s">
-        <v>91</v>
-      </c>
-      <c r="F42" t="s">
+      <c r="H42" t="s">
         <v>232</v>
-      </c>
-      <c r="G42" t="s">
-        <v>227</v>
-      </c>
-      <c r="H42" t="s">
-        <v>233</v>
       </c>
     </row>
     <row r="43" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
+        <v>233</v>
+      </c>
+      <c r="B43" t="s">
+        <v>9</v>
+      </c>
+      <c r="C43" t="s">
         <v>234</v>
-      </c>
-      <c r="B43" t="s">
-        <v>9</v>
-      </c>
-      <c r="C43" t="s">
-        <v>235</v>
       </c>
       <c r="D43" t="s">
         <v>11</v>
@@ -2555,47 +2924,47 @@
         <v>18</v>
       </c>
       <c r="F43" t="s">
+        <v>235</v>
+      </c>
+      <c r="G43" t="s">
         <v>236</v>
       </c>
-      <c r="G43" t="s">
+      <c r="H43" t="s">
         <v>237</v>
-      </c>
-      <c r="H43" t="s">
-        <v>238</v>
       </c>
     </row>
     <row r="44" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
+        <v>238</v>
+      </c>
+      <c r="B44" t="s">
+        <v>9</v>
+      </c>
+      <c r="C44" t="s">
         <v>239</v>
       </c>
-      <c r="B44" t="s">
-        <v>9</v>
-      </c>
-      <c r="C44" t="s">
+      <c r="D44" t="s">
+        <v>11</v>
+      </c>
+      <c r="E44" t="s">
+        <v>12</v>
+      </c>
+      <c r="F44" t="s">
         <v>240</v>
       </c>
-      <c r="D44" t="s">
-        <v>11</v>
-      </c>
-      <c r="E44" t="s">
-        <v>18</v>
-      </c>
-      <c r="F44" t="s">
+      <c r="G44" t="s">
         <v>241</v>
       </c>
-      <c r="G44" t="s">
+      <c r="H44" t="s">
         <v>242</v>
-      </c>
-      <c r="H44" t="s">
-        <v>243</v>
       </c>
     </row>
     <row r="45" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
+        <v>243</v>
+      </c>
+      <c r="B45" t="s">
         <v>244</v>
-      </c>
-      <c r="B45" t="s">
-        <v>9</v>
       </c>
       <c r="C45" t="s">
         <v>245</v>
@@ -2621,7 +2990,7 @@
         <v>249</v>
       </c>
       <c r="B46" t="s">
-        <v>9</v>
+        <v>22</v>
       </c>
       <c r="C46" t="s">
         <v>250</v>
@@ -2630,7 +2999,7 @@
         <v>11</v>
       </c>
       <c r="E46" t="s">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="F46" t="s">
         <v>251</v>
@@ -2656,7 +3025,7 @@
         <v>11</v>
       </c>
       <c r="E47" t="s">
-        <v>12</v>
+        <v>91</v>
       </c>
       <c r="F47" t="s">
         <v>256</v>
@@ -2673,62 +3042,62 @@
         <v>259</v>
       </c>
       <c r="B48" t="s">
-        <v>9</v>
+        <v>260</v>
       </c>
       <c r="C48" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="D48" t="s">
         <v>11</v>
       </c>
       <c r="E48" t="s">
-        <v>12</v>
+        <v>91</v>
       </c>
       <c r="F48" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="G48" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="H48" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
     </row>
     <row r="49" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="B49" t="s">
-        <v>9</v>
+        <v>266</v>
       </c>
       <c r="C49" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="D49" t="s">
         <v>11</v>
       </c>
       <c r="E49" t="s">
-        <v>12</v>
+        <v>91</v>
       </c>
       <c r="F49" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="G49" t="s">
-        <v>267</v>
+        <v>263</v>
       </c>
       <c r="H49" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
     </row>
     <row r="50" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="B50" t="s">
         <v>9</v>
       </c>
       <c r="C50" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="D50" t="s">
         <v>11</v>
@@ -2737,21 +3106,21 @@
         <v>18</v>
       </c>
       <c r="F50" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="G50" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="H50" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
     </row>
     <row r="51" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="B51" t="s">
-        <v>275</v>
+        <v>9</v>
       </c>
       <c r="C51" t="s">
         <v>276</v>
@@ -2760,7 +3129,7 @@
         <v>11</v>
       </c>
       <c r="E51" t="s">
-        <v>91</v>
+        <v>18</v>
       </c>
       <c r="F51" t="s">
         <v>277</v>
@@ -2786,7 +3155,7 @@
         <v>11</v>
       </c>
       <c r="E52" t="s">
-        <v>91</v>
+        <v>30</v>
       </c>
       <c r="F52" t="s">
         <v>282</v>
@@ -2838,7 +3207,7 @@
         <v>11</v>
       </c>
       <c r="E54" t="s">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="F54" t="s">
         <v>292</v>
@@ -2864,7 +3233,7 @@
         <v>11</v>
       </c>
       <c r="E55" t="s">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="F55" t="s">
         <v>297</v>
@@ -2890,7 +3259,7 @@
         <v>11</v>
       </c>
       <c r="E56" t="s">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="F56" t="s">
         <v>302</v>
@@ -2916,7 +3285,7 @@
         <v>11</v>
       </c>
       <c r="E57" t="s">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="F57" t="s">
         <v>307</v>
@@ -2933,88 +3302,88 @@
         <v>310</v>
       </c>
       <c r="B58" t="s">
-        <v>9</v>
+        <v>311</v>
       </c>
       <c r="C58" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="D58" t="s">
         <v>11</v>
       </c>
       <c r="E58" t="s">
-        <v>18</v>
+        <v>91</v>
       </c>
       <c r="F58" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="G58" t="s">
-        <v>59</v>
+        <v>314</v>
       </c>
       <c r="H58" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
     </row>
     <row r="59" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="B59" t="s">
         <v>9</v>
       </c>
       <c r="C59" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="D59" t="s">
         <v>11</v>
       </c>
       <c r="E59" t="s">
-        <v>30</v>
+        <v>91</v>
       </c>
       <c r="F59" t="s">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="G59" t="s">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="H59" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
     </row>
     <row r="60" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="B60" t="s">
-        <v>213</v>
+        <v>9</v>
       </c>
       <c r="C60" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="D60" t="s">
         <v>11</v>
       </c>
       <c r="E60" t="s">
-        <v>30</v>
+        <v>12</v>
       </c>
       <c r="F60" t="s">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="G60" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="H60" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
     </row>
     <row r="61" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="B61" t="s">
         <v>9</v>
       </c>
       <c r="C61" t="s">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="D61" t="s">
         <v>11</v>
@@ -3023,24 +3392,24 @@
         <v>18</v>
       </c>
       <c r="F61" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="G61" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="H61" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
     </row>
     <row r="62" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="B62" t="s">
         <v>9</v>
       </c>
       <c r="C62" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="D62" t="s">
         <v>11</v>
@@ -3049,24 +3418,24 @@
         <v>18</v>
       </c>
       <c r="F62" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="G62" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="H62" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
     </row>
     <row r="63" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="B63" t="s">
         <v>9</v>
       </c>
       <c r="C63" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="D63" t="s">
         <v>11</v>
@@ -3075,65 +3444,689 @@
         <v>18</v>
       </c>
       <c r="F63" t="s">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="G63" t="s">
-        <v>14</v>
+        <v>339</v>
       </c>
       <c r="H63" t="s">
-        <v>337</v>
+        <v>340</v>
       </c>
     </row>
     <row r="64" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
-        <v>338</v>
+        <v>341</v>
       </c>
       <c r="B64" t="s">
         <v>9</v>
       </c>
       <c r="C64" t="s">
-        <v>339</v>
+        <v>342</v>
       </c>
       <c r="D64" t="s">
         <v>11</v>
       </c>
       <c r="E64" t="s">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="F64" t="s">
-        <v>340</v>
+        <v>343</v>
       </c>
       <c r="G64" t="s">
-        <v>14</v>
+        <v>344</v>
       </c>
       <c r="H64" t="s">
-        <v>341</v>
+        <v>345</v>
       </c>
     </row>
     <row r="65" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
-        <v>342</v>
+        <v>346</v>
       </c>
       <c r="B65" t="s">
-        <v>9</v>
+        <v>22</v>
       </c>
       <c r="C65" t="s">
-        <v>343</v>
+        <v>347</v>
       </c>
       <c r="D65" t="s">
         <v>11</v>
       </c>
       <c r="E65" t="s">
+        <v>24</v>
+      </c>
+      <c r="F65" t="s">
+        <v>348</v>
+      </c>
+      <c r="G65" t="s">
+        <v>349</v>
+      </c>
+      <c r="H65" t="s">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="66" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A66" t="s">
+        <v>351</v>
+      </c>
+      <c r="B66" t="s">
+        <v>9</v>
+      </c>
+      <c r="C66" t="s">
+        <v>352</v>
+      </c>
+      <c r="D66" t="s">
+        <v>11</v>
+      </c>
+      <c r="E66" t="s">
         <v>12</v>
       </c>
-      <c r="F65" t="s">
-        <v>344</v>
-      </c>
-      <c r="G65" t="s">
-        <v>262</v>
-      </c>
-      <c r="H65" t="s">
-        <v>345</v>
+      <c r="F66" t="s">
+        <v>353</v>
+      </c>
+      <c r="G66" t="s">
+        <v>354</v>
+      </c>
+      <c r="H66" t="s">
+        <v>355</v>
+      </c>
+    </row>
+    <row r="67" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A67" t="s">
+        <v>356</v>
+      </c>
+      <c r="B67" t="s">
+        <v>357</v>
+      </c>
+      <c r="C67" t="s">
+        <v>358</v>
+      </c>
+      <c r="D67" t="s">
+        <v>11</v>
+      </c>
+      <c r="E67" t="s">
+        <v>24</v>
+      </c>
+      <c r="F67" t="s">
+        <v>359</v>
+      </c>
+      <c r="G67" t="s">
+        <v>360</v>
+      </c>
+      <c r="H67" t="s">
+        <v>361</v>
+      </c>
+    </row>
+    <row r="68" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A68" t="s">
+        <v>362</v>
+      </c>
+      <c r="B68" t="s">
+        <v>9</v>
+      </c>
+      <c r="C68" t="s">
+        <v>363</v>
+      </c>
+      <c r="D68" t="s">
+        <v>11</v>
+      </c>
+      <c r="E68" t="s">
+        <v>18</v>
+      </c>
+      <c r="F68" t="s">
+        <v>364</v>
+      </c>
+      <c r="G68" t="s">
+        <v>59</v>
+      </c>
+      <c r="H68" t="s">
+        <v>365</v>
+      </c>
+    </row>
+    <row r="69" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A69" t="s">
+        <v>366</v>
+      </c>
+      <c r="B69" t="s">
+        <v>9</v>
+      </c>
+      <c r="C69" t="s">
+        <v>367</v>
+      </c>
+      <c r="D69" t="s">
+        <v>11</v>
+      </c>
+      <c r="E69" t="s">
+        <v>30</v>
+      </c>
+      <c r="F69" t="s">
+        <v>368</v>
+      </c>
+      <c r="G69" t="s">
+        <v>369</v>
+      </c>
+      <c r="H69" t="s">
+        <v>370</v>
+      </c>
+    </row>
+    <row r="70" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A70" t="s">
+        <v>371</v>
+      </c>
+      <c r="B70" t="s">
+        <v>244</v>
+      </c>
+      <c r="C70" t="s">
+        <v>372</v>
+      </c>
+      <c r="D70" t="s">
+        <v>11</v>
+      </c>
+      <c r="E70" t="s">
+        <v>30</v>
+      </c>
+      <c r="F70" t="s">
+        <v>373</v>
+      </c>
+      <c r="G70" t="s">
+        <v>374</v>
+      </c>
+      <c r="H70" t="s">
+        <v>375</v>
+      </c>
+    </row>
+    <row r="71" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A71" t="s">
+        <v>376</v>
+      </c>
+      <c r="B71" t="s">
+        <v>9</v>
+      </c>
+      <c r="C71" t="s">
+        <v>377</v>
+      </c>
+      <c r="D71" t="s">
+        <v>11</v>
+      </c>
+      <c r="E71" t="s">
+        <v>24</v>
+      </c>
+      <c r="F71" t="s">
+        <v>378</v>
+      </c>
+      <c r="G71" t="s">
+        <v>379</v>
+      </c>
+      <c r="H71" t="s">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="72" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A72" t="s">
+        <v>381</v>
+      </c>
+      <c r="B72" t="s">
+        <v>9</v>
+      </c>
+      <c r="C72" t="s">
+        <v>382</v>
+      </c>
+      <c r="D72" t="s">
+        <v>11</v>
+      </c>
+      <c r="E72" t="s">
+        <v>18</v>
+      </c>
+      <c r="F72" t="s">
+        <v>383</v>
+      </c>
+      <c r="G72" t="s">
+        <v>384</v>
+      </c>
+      <c r="H72" t="s">
+        <v>385</v>
+      </c>
+    </row>
+    <row r="73" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A73" t="s">
+        <v>386</v>
+      </c>
+      <c r="B73" t="s">
+        <v>9</v>
+      </c>
+      <c r="C73" t="s">
+        <v>387</v>
+      </c>
+      <c r="D73" t="s">
+        <v>11</v>
+      </c>
+      <c r="E73" t="s">
+        <v>12</v>
+      </c>
+      <c r="F73" t="s">
+        <v>388</v>
+      </c>
+      <c r="G73" t="s">
+        <v>389</v>
+      </c>
+      <c r="H73" t="s">
+        <v>390</v>
+      </c>
+    </row>
+    <row r="74" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A74" t="s">
+        <v>391</v>
+      </c>
+      <c r="B74" t="s">
+        <v>9</v>
+      </c>
+      <c r="C74" t="s">
+        <v>392</v>
+      </c>
+      <c r="D74" t="s">
+        <v>11</v>
+      </c>
+      <c r="E74" t="s">
+        <v>12</v>
+      </c>
+      <c r="F74" t="s">
+        <v>393</v>
+      </c>
+      <c r="G74" t="s">
+        <v>394</v>
+      </c>
+      <c r="H74" t="s">
+        <v>395</v>
+      </c>
+    </row>
+    <row r="75" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A75" t="s">
+        <v>396</v>
+      </c>
+      <c r="B75" t="s">
+        <v>9</v>
+      </c>
+      <c r="C75" t="s">
+        <v>397</v>
+      </c>
+      <c r="D75" t="s">
+        <v>11</v>
+      </c>
+      <c r="E75" t="s">
+        <v>12</v>
+      </c>
+      <c r="F75" t="s">
+        <v>398</v>
+      </c>
+      <c r="G75" t="s">
+        <v>399</v>
+      </c>
+      <c r="H75" t="s">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="76" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A76" t="s">
+        <v>401</v>
+      </c>
+      <c r="B76" t="s">
+        <v>9</v>
+      </c>
+      <c r="C76" t="s">
+        <v>402</v>
+      </c>
+      <c r="D76" t="s">
+        <v>11</v>
+      </c>
+      <c r="E76" t="s">
+        <v>12</v>
+      </c>
+      <c r="F76" t="s">
+        <v>403</v>
+      </c>
+      <c r="G76" t="s">
+        <v>404</v>
+      </c>
+      <c r="H76" t="s">
+        <v>405</v>
+      </c>
+    </row>
+    <row r="77" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A77" t="s">
+        <v>406</v>
+      </c>
+      <c r="B77" t="s">
+        <v>9</v>
+      </c>
+      <c r="C77" t="s">
+        <v>407</v>
+      </c>
+      <c r="D77" t="s">
+        <v>11</v>
+      </c>
+      <c r="E77" t="s">
+        <v>24</v>
+      </c>
+      <c r="F77" t="s">
+        <v>408</v>
+      </c>
+      <c r="G77" t="s">
+        <v>409</v>
+      </c>
+      <c r="H77" t="s">
+        <v>410</v>
+      </c>
+    </row>
+    <row r="78" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A78" t="s">
+        <v>411</v>
+      </c>
+      <c r="B78" t="s">
+        <v>163</v>
+      </c>
+      <c r="C78" t="s">
+        <v>412</v>
+      </c>
+      <c r="D78" t="s">
+        <v>11</v>
+      </c>
+      <c r="E78" t="s">
+        <v>24</v>
+      </c>
+      <c r="F78" t="s">
+        <v>413</v>
+      </c>
+      <c r="G78" t="s">
+        <v>414</v>
+      </c>
+      <c r="H78" t="s">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="79" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A79" t="s">
+        <v>416</v>
+      </c>
+      <c r="B79" t="s">
+        <v>9</v>
+      </c>
+      <c r="C79" t="s">
+        <v>417</v>
+      </c>
+      <c r="D79" t="s">
+        <v>11</v>
+      </c>
+      <c r="E79" t="s">
+        <v>12</v>
+      </c>
+      <c r="F79" t="s">
+        <v>418</v>
+      </c>
+      <c r="G79" t="s">
+        <v>419</v>
+      </c>
+      <c r="H79" t="s">
+        <v>420</v>
+      </c>
+    </row>
+    <row r="80" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A80" t="s">
+        <v>421</v>
+      </c>
+      <c r="B80" t="s">
+        <v>9</v>
+      </c>
+      <c r="C80" t="s">
+        <v>422</v>
+      </c>
+      <c r="D80" t="s">
+        <v>11</v>
+      </c>
+      <c r="E80" t="s">
+        <v>12</v>
+      </c>
+      <c r="F80" t="s">
+        <v>423</v>
+      </c>
+      <c r="G80" t="s">
+        <v>424</v>
+      </c>
+      <c r="H80" t="s">
+        <v>425</v>
+      </c>
+    </row>
+    <row r="81" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A81" t="s">
+        <v>426</v>
+      </c>
+      <c r="B81" t="s">
+        <v>9</v>
+      </c>
+      <c r="C81" t="s">
+        <v>427</v>
+      </c>
+      <c r="D81" t="s">
+        <v>11</v>
+      </c>
+      <c r="E81" t="s">
+        <v>12</v>
+      </c>
+      <c r="F81" t="s">
+        <v>428</v>
+      </c>
+      <c r="G81" t="s">
+        <v>429</v>
+      </c>
+      <c r="H81" t="s">
+        <v>430</v>
+      </c>
+    </row>
+    <row r="82" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A82" t="s">
+        <v>431</v>
+      </c>
+      <c r="B82" t="s">
+        <v>9</v>
+      </c>
+      <c r="C82" t="s">
+        <v>432</v>
+      </c>
+      <c r="D82" t="s">
+        <v>11</v>
+      </c>
+      <c r="E82" t="s">
+        <v>24</v>
+      </c>
+      <c r="F82" t="s">
+        <v>433</v>
+      </c>
+      <c r="G82" t="s">
+        <v>434</v>
+      </c>
+      <c r="H82" t="s">
+        <v>435</v>
+      </c>
+    </row>
+    <row r="83" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A83" t="s">
+        <v>436</v>
+      </c>
+      <c r="B83" t="s">
+        <v>9</v>
+      </c>
+      <c r="C83" t="s">
+        <v>437</v>
+      </c>
+      <c r="D83" t="s">
+        <v>11</v>
+      </c>
+      <c r="E83" t="s">
+        <v>24</v>
+      </c>
+      <c r="F83" t="s">
+        <v>438</v>
+      </c>
+      <c r="G83" t="s">
+        <v>439</v>
+      </c>
+      <c r="H83" t="s">
+        <v>440</v>
+      </c>
+    </row>
+    <row r="84" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A84" t="s">
+        <v>441</v>
+      </c>
+      <c r="B84" t="s">
+        <v>442</v>
+      </c>
+      <c r="C84" t="s">
+        <v>443</v>
+      </c>
+      <c r="D84" t="s">
+        <v>11</v>
+      </c>
+      <c r="E84" t="s">
+        <v>24</v>
+      </c>
+      <c r="F84" t="s">
+        <v>444</v>
+      </c>
+      <c r="G84" t="s">
+        <v>445</v>
+      </c>
+      <c r="H84" t="s">
+        <v>446</v>
+      </c>
+    </row>
+    <row r="85" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A85" t="s">
+        <v>447</v>
+      </c>
+      <c r="B85" t="s">
+        <v>442</v>
+      </c>
+      <c r="C85" t="s">
+        <v>448</v>
+      </c>
+      <c r="D85" t="s">
+        <v>11</v>
+      </c>
+      <c r="E85" t="s">
+        <v>24</v>
+      </c>
+      <c r="F85" t="s">
+        <v>449</v>
+      </c>
+      <c r="G85" t="s">
+        <v>450</v>
+      </c>
+      <c r="H85" t="s">
+        <v>451</v>
+      </c>
+    </row>
+    <row r="86" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A86" t="s">
+        <v>452</v>
+      </c>
+      <c r="B86" t="s">
+        <v>9</v>
+      </c>
+      <c r="C86" t="s">
+        <v>453</v>
+      </c>
+      <c r="D86" t="s">
+        <v>11</v>
+      </c>
+      <c r="E86" t="s">
+        <v>18</v>
+      </c>
+      <c r="F86" t="s">
+        <v>454</v>
+      </c>
+      <c r="G86" t="s">
+        <v>455</v>
+      </c>
+      <c r="H86" t="s">
+        <v>456</v>
+      </c>
+    </row>
+    <row r="87" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A87" t="s">
+        <v>457</v>
+      </c>
+      <c r="B87" t="s">
+        <v>9</v>
+      </c>
+      <c r="C87" t="s">
+        <v>458</v>
+      </c>
+      <c r="D87" t="s">
+        <v>11</v>
+      </c>
+      <c r="E87" t="s">
+        <v>18</v>
+      </c>
+      <c r="F87" t="s">
+        <v>459</v>
+      </c>
+      <c r="G87" t="s">
+        <v>14</v>
+      </c>
+      <c r="H87" t="s">
+        <v>460</v>
+      </c>
+    </row>
+    <row r="88" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A88" t="s">
+        <v>461</v>
+      </c>
+      <c r="B88" t="s">
+        <v>9</v>
+      </c>
+      <c r="C88" t="s">
+        <v>462</v>
+      </c>
+      <c r="D88" t="s">
+        <v>11</v>
+      </c>
+      <c r="E88" t="s">
+        <v>18</v>
+      </c>
+      <c r="F88" t="s">
+        <v>463</v>
+      </c>
+      <c r="G88" t="s">
+        <v>14</v>
+      </c>
+      <c r="H88" t="s">
+        <v>464</v>
+      </c>
+    </row>
+    <row r="89" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A89" t="s">
+        <v>465</v>
+      </c>
+      <c r="B89" t="s">
+        <v>9</v>
+      </c>
+      <c r="C89" t="s">
+        <v>466</v>
+      </c>
+      <c r="D89" t="s">
+        <v>11</v>
+      </c>
+      <c r="E89" t="s">
+        <v>12</v>
+      </c>
+      <c r="F89" t="s">
+        <v>467</v>
+      </c>
+      <c r="G89" t="s">
+        <v>298</v>
+      </c>
+      <c r="H89" t="s">
+        <v>468</v>
       </c>
     </row>
   </sheetData>
